--- a/HALO.xlsx
+++ b/HALO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CDCD7A-BC84-414D-8AF0-2112101030D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5959D3-0AB1-45AD-A910-68CA7E32B95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27015" yWindow="750" windowWidth="26490" windowHeight="19650" activeTab="1" xr2:uid="{EFBABCF6-2DC2-4552-B0BE-FF1FC4AE1F86}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="19050" windowHeight="19840" xr2:uid="{EFBABCF6-2DC2-4552-B0BE-FF1FC4AE1F86}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>Price</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>Q424</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -676,9 +679,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF115ACB-227D-4711-83D3-8545DAAED56E}">
   <dimension ref="B2:N18"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>38</v>
       </c>
@@ -686,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>63.69</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+        <v>82.57</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>39</v>
       </c>
@@ -697,13 +700,13 @@
         <v>1</v>
       </c>
       <c r="M3" s="2">
-        <v>126.678</v>
+        <v>118.613</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>40</v>
       </c>
@@ -712,10 +715,10 @@
       </c>
       <c r="M4" s="2">
         <f>+M2*M3</f>
-        <v>8068.1218199999994</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+        <v>9793.8754099999987</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>50</v>
       </c>
@@ -723,14 +726,14 @@
         <v>3</v>
       </c>
       <c r="M5" s="2">
-        <f>187.864+341.166</f>
-        <v>529.03</v>
+        <f>309.749+8.873</f>
+        <v>318.62200000000001</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>51</v>
       </c>
@@ -738,13 +741,14 @@
         <v>4</v>
       </c>
       <c r="M6" s="2">
-        <v>1502.5150000000001</v>
+        <f>1935.896+208.743</f>
+        <v>2144.6390000000001</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>41</v>
       </c>
@@ -753,45 +757,45 @@
       </c>
       <c r="M7" s="2">
         <f>+M4-M5+M6</f>
-        <v>9041.6068199999991</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+        <v>11619.89241</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H18" t="s">
         <v>42</v>
       </c>
@@ -804,19 +808,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB087919-4803-4438-BCF8-90C3F9DFA3FB}">
   <dimension ref="A1:AH18"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="21" width="9.140625" style="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="21" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
@@ -917,7 +921,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
@@ -953,7 +957,7 @@
         <v>99.551000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
@@ -985,7 +989,7 @@
         <v>61.427</v>
       </c>
     </row>
-    <row r="5" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1017,7 +1021,7 @@
         <v>47.997999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
@@ -1051,7 +1055,7 @@
         <v>208.976</v>
       </c>
     </row>
-    <row r="7" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
@@ -1079,7 +1083,7 @@
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
     </row>
-    <row r="8" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
@@ -1109,7 +1113,7 @@
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
     </row>
-    <row r="9" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
@@ -1137,7 +1141,7 @@
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
     </row>
-    <row r="10" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
@@ -1165,7 +1169,7 @@
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
     </row>
-    <row r="11" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
@@ -1195,7 +1199,7 @@
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
     </row>
-    <row r="12" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
@@ -1225,7 +1229,7 @@
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
     </row>
-    <row r="13" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
@@ -1255,7 +1259,7 @@
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
     </row>
-    <row r="14" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
@@ -1285,7 +1289,7 @@
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>35</v>
       </c>
@@ -1296,7 +1300,7 @@
         <v>12.073</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>36</v>
       </c>
@@ -1309,7 +1313,7 @@
         <v>91.538999999999987</v>
       </c>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>37</v>
       </c>
@@ -1322,7 +1326,7 @@
         <v>0.65672551959651893</v>
       </c>
     </row>
-    <row r="18" spans="2:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>1</v>
       </c>
